--- a/stories/arbres/TREE-SEC-008.xlsx
+++ b/stories/arbres/TREE-SEC-008.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Lina est au parc. Maman est là. Papa est là aussi. La maîtresse est près du portail. Si Lina cherche, elle va vers Papa. Ou vers Maman. Ou vers la maîtresse. Les pieds vont vers eux. Les mains tiennent la main de Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lina voit le chat. Elle cherche. Elle va vers Papa. Ou vers Maman. Ou vers la maîtresse. Les pieds vont vers eux.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On va vers qui ? Papa, maman, ou la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2046,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina retient : papa, maman, maîtresse. Les mains peuvent tenir la main de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2237,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2361,6 +2408,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le bac à sable. Un oiseau chante. Lina va au bac à sable. Elle reste près de Maman. Ou Papa. Ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2549,6 +2601,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2717,6 +2774,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. Le vent est doux. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2879,6 +2941,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3045,6 +3112,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. Un vélo sonne loin. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3207,6 +3279,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3373,6 +3450,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. Le sable est frais. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3535,6 +3617,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3701,6 +3788,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le toboggan. Le bac gratte. Lina va près du toboggan. Elle va vers Papa, Maman, ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3889,6 +3981,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -4057,6 +4154,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. Un vélo sonne loin. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4219,6 +4321,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4385,6 +4492,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. Le sable est frais. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4547,6 +4659,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4713,6 +4830,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. On rit un peu. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4875,6 +4997,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5041,6 +5168,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi les balançoires. Le vent est doux. Lina va près des balançoires. Elle va vers Papa, Maman, ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5229,6 +5361,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5397,6 +5534,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. Le sable est frais. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5559,6 +5701,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5725,6 +5872,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. On rit un peu. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5887,6 +6039,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6053,6 +6210,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. Un oiseau chante. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6215,6 +6377,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6381,6 +6548,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lina voit le chien. Elle cherche. Elle va vers Papa. Ou vers Maman. Ou vers la maîtresse. Les pieds vont vers eux.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6565,6 +6737,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On va vers qui ? Papa, maman, ou la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -6737,6 +6914,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina retient : papa, maman, maîtresse. Les mains peuvent tenir la main de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6923,6 +7105,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7089,6 +7276,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le bac à sable. Un vélo sonne loin. Lina va au bac à sable. Elle reste près de Maman. Ou Papa. Ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7277,6 +7469,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -7445,6 +7642,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. Un vélo sonne loin. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7607,6 +7809,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7773,6 +7980,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. Le sable est frais. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7935,6 +8147,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8101,6 +8318,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. On rit un peu. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8263,6 +8485,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8429,6 +8656,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le toboggan. Le sable est frais. Lina va près du toboggan. Elle va vers Papa, Maman, ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8617,6 +8849,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8785,6 +9022,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. Le sable est frais. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8947,6 +9189,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9113,6 +9360,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. On rit un peu. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9275,6 +9527,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9441,6 +9698,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. Un oiseau chante. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9603,6 +9865,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9769,6 +10036,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi les balançoires. On rit un peu. Lina va près des balançoires. Elle va vers Papa, Maman, ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9957,6 +10229,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -10125,6 +10402,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. On rit un peu. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10287,6 +10569,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10453,6 +10740,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. Un oiseau chante. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10615,6 +10907,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10781,6 +11078,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. Le bac gratte. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10943,6 +11245,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11109,6 +11416,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lina voit la poule. Elle cherche. Elle va vers Papa. Ou vers Maman. Ou vers la maîtresse. Les pieds vont vers eux.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11293,6 +11605,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On va vers qui ? Papa, maman, ou la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -11465,6 +11782,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina retient : papa, maman, maîtresse. Les mains peuvent tenir la main de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11651,6 +11973,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11817,6 +12144,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le bac à sable. Un oiseau chante. Lina va au bac à sable. Elle reste près de Maman. Ou Papa. Ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12005,6 +12337,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12173,6 +12510,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. Le sable est frais. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12335,6 +12677,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12501,6 +12848,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. On rit un peu. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12663,6 +13015,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12829,6 +13186,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. Un oiseau chante. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12991,6 +13353,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13157,6 +13524,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le toboggan. Le bac gratte. Lina va près du toboggan. Elle va vers Papa, Maman, ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13345,6 +13717,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -13513,6 +13890,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. On rit un peu. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13675,6 +14057,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13841,6 +14228,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. Un oiseau chante. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14003,6 +14395,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14169,6 +14566,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. Le bac gratte. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14331,6 +14733,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14497,6 +14904,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi les balançoires. Le vent est doux. Lina va près des balançoires. Elle va vers Papa, Maman, ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14685,6 +15097,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14853,6 +15270,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. Un oiseau chante. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15015,6 +15437,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15181,6 +15608,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. Le bac gratte. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15343,6 +15775,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15509,6 +15946,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. Le vent est doux. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15671,6 +16113,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15689,7 +16136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15762,6 +16209,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-008.xlsx
+++ b/stories/arbres/TREE-SEC-008.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,11 @@
           <t>narrateur|Aujourd'hui, Lina est au parc. Maman est là. Papa est là aussi. La maîtresse est près du portail. Si Lina cherche, elle va vers Papa. Ou vers Maman. Ou vers la maîtresse. Les pieds vont vers eux. Les mains tiennent la main de Maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1512,6 +1522,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1685,6 +1700,7 @@
           <t>narrateur|Lina voit le chat. Elle cherche. Elle va vers Papa. Ou vers Maman. Ou vers la maîtresse. Les pieds vont vers eux.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1892,7 @@
           <t>narrateur|On va vers qui ? Papa, maman, ou la maîtresse.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2051,6 +2068,7 @@
           <t>narrateur|Oui. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina retient : papa, maman, maîtresse. Les mains peuvent tenir la main de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2242,6 +2260,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2413,6 +2432,7 @@
           <t>narrateur|Lina a choisi le bac à sable. Un oiseau chante. Lina va au bac à sable. Elle reste près de Maman. Ou Papa. Ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2608,6 +2628,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2779,6 +2800,7 @@
           <t>narrateur|Lina choisit rouge. Le vent est doux. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2946,6 +2968,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3117,6 +3140,7 @@
           <t>narrateur|Lina choisit bleu. Un vélo sonne loin. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3284,6 +3308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3455,6 +3480,7 @@
           <t>narrateur|Lina choisit vert. Le sable est frais. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3622,6 +3648,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3793,6 +3820,7 @@
           <t>narrateur|Lina a choisi le toboggan. Le bac gratte. Lina va près du toboggan. Elle va vers Papa, Maman, ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3988,6 +4016,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4159,6 +4188,7 @@
           <t>narrateur|Lina choisit rouge. Un vélo sonne loin. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4326,6 +4356,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4497,6 +4528,7 @@
           <t>narrateur|Lina choisit bleu. Le sable est frais. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4664,6 +4696,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4835,6 +4868,7 @@
           <t>narrateur|Lina choisit vert. On rit un peu. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5002,6 +5036,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5173,6 +5208,7 @@
           <t>narrateur|Lina a choisi les balançoires. Le vent est doux. Lina va près des balançoires. Elle va vers Papa, Maman, ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5368,6 +5404,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5539,6 +5576,7 @@
           <t>narrateur|Lina choisit rouge. Le sable est frais. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5706,6 +5744,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5877,6 +5916,7 @@
           <t>narrateur|Lina choisit bleu. On rit un peu. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6044,6 +6084,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6215,6 +6256,7 @@
           <t>narrateur|Lina choisit vert. Un oiseau chante. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6382,6 +6424,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6553,6 +6596,11 @@
           <t>narrateur|Lina voit le chien. Elle cherche. Elle va vers Papa. Ou vers Maman. Ou vers la maîtresse. Les pieds vont vers eux.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6744,6 +6792,7 @@
           <t>narrateur|On va vers qui ? Papa, maman, ou la maîtresse.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6919,6 +6968,7 @@
           <t>narrateur|Oui. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina retient : papa, maman, maîtresse. Les mains peuvent tenir la main de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7110,6 +7160,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7281,6 +7332,7 @@
           <t>narrateur|Lina a choisi le bac à sable. Un vélo sonne loin. Lina va au bac à sable. Elle reste près de Maman. Ou Papa. Ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7476,6 +7528,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7647,6 +7700,7 @@
           <t>narrateur|Lina choisit rouge. Un vélo sonne loin. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7814,6 +7868,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7985,6 +8040,7 @@
           <t>narrateur|Lina choisit bleu. Le sable est frais. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8152,6 +8208,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8323,6 +8380,7 @@
           <t>narrateur|Lina choisit vert. On rit un peu. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8490,6 +8548,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8661,6 +8720,7 @@
           <t>narrateur|Lina a choisi le toboggan. Le sable est frais. Lina va près du toboggan. Elle va vers Papa, Maman, ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8856,6 +8916,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9027,6 +9088,7 @@
           <t>narrateur|Lina choisit rouge. Le sable est frais. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9194,6 +9256,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9365,6 +9428,7 @@
           <t>narrateur|Lina choisit bleu. On rit un peu. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9532,6 +9596,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9703,6 +9768,7 @@
           <t>narrateur|Lina choisit vert. Un oiseau chante. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9870,6 +9936,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10041,6 +10108,7 @@
           <t>narrateur|Lina a choisi les balançoires. On rit un peu. Lina va près des balançoires. Elle va vers Papa, Maman, ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10236,6 +10304,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10407,6 +10476,7 @@
           <t>narrateur|Lina choisit rouge. On rit un peu. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10574,6 +10644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10745,6 +10816,7 @@
           <t>narrateur|Lina choisit bleu. Un oiseau chante. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10912,6 +10984,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11083,6 +11156,7 @@
           <t>narrateur|Lina choisit vert. Le bac gratte. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11250,6 +11324,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11421,6 +11496,7 @@
           <t>narrateur|Lina voit la poule. Elle cherche. Elle va vers Papa. Ou vers Maman. Ou vers la maîtresse. Les pieds vont vers eux.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11612,6 +11688,7 @@
           <t>narrateur|On va vers qui ? Papa, maman, ou la maîtresse.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11787,6 +11864,7 @@
           <t>narrateur|Oui. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina retient : papa, maman, maîtresse. Les mains peuvent tenir la main de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11978,6 +12056,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12149,6 +12228,7 @@
           <t>narrateur|Lina a choisi le bac à sable. Un oiseau chante. Lina va au bac à sable. Elle reste près de Maman. Ou Papa. Ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12344,6 +12424,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12515,6 +12596,7 @@
           <t>narrateur|Lina choisit rouge. Le sable est frais. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12682,6 +12764,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12853,6 +12936,7 @@
           <t>narrateur|Lina choisit bleu. On rit un peu. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13020,6 +13104,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13191,6 +13276,7 @@
           <t>narrateur|Lina choisit vert. Un oiseau chante. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13358,6 +13444,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13529,6 +13616,7 @@
           <t>narrateur|Lina a choisi le toboggan. Le bac gratte. Lina va près du toboggan. Elle va vers Papa, Maman, ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13724,6 +13812,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13895,6 +13984,7 @@
           <t>narrateur|Lina choisit rouge. On rit un peu. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14062,6 +14152,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14233,6 +14324,7 @@
           <t>narrateur|Lina choisit bleu. Un oiseau chante. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14400,6 +14492,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14571,6 +14664,7 @@
           <t>narrateur|Lina choisit vert. Le bac gratte. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14738,6 +14832,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14909,6 +15004,7 @@
           <t>narrateur|Lina a choisi les balançoires. Le vent est doux. Lina va près des balançoires. Elle va vers Papa, Maman, ou la maîtresse. Les mains peuvent tenir la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15104,6 +15200,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15275,6 +15372,7 @@
           <t>narrateur|Lina choisit rouge. Un oiseau chante. Lina prend le seau rouge. Elle va vers Maman. Papa et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15442,6 +15540,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15613,6 +15712,7 @@
           <t>narrateur|Lina choisit bleu. Le bac gratte. Lina prend le seau bleu. Elle va vers Papa. Maman et la maîtresse sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15780,6 +15880,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15951,6 +16052,7 @@
           <t>narrateur|Lina choisit vert. Le vent est doux. Lina prend le seau vert. Elle va vers la maîtresse. Papa et Maman sont là. On va vers Papa, ou vers Maman, ou vers la maîtresse. Les pieds vont vers eux. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16118,6 +16220,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16136,7 +16239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16216,6 +16319,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16230,7 +16347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16417,6 +16534,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
